--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="35">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>OFF-SCREEN TASKS</t>
+  </si>
+  <si>
+    <t>REGULAR WORKING DAY</t>
   </si>
 </sst>
 </file>
@@ -163,18 +166,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -184,7 +181,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -201,37 +198,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -241,9 +218,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -562,7 +565,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -580,48 +583,48 @@
     <col min="14" max="14" width="31.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="11" customFormat="1" ht="13.8">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:14" s="17" customFormat="1" ht="13.8">
+      <c r="A1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="4"/>
-    </row>
-    <row r="2" spans="1:14" s="11" customFormat="1" ht="13.8">
-      <c r="A2" s="3" t="s">
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="10"/>
+    </row>
+    <row r="2" spans="1:14" s="17" customFormat="1" ht="13.8">
+      <c r="A2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="4"/>
-    </row>
-    <row r="4" spans="1:14" s="12" customFormat="1" ht="52.2">
-      <c r="A4" s="5" t="s">
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="10"/>
+    </row>
+    <row r="4" spans="1:14" s="4" customFormat="1" ht="52.2">
+      <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -664,549 +667,577 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="13" customFormat="1">
-      <c r="A5" s="8">
+    <row r="5" spans="1:14" s="5" customFormat="1">
+      <c r="A5" s="11">
         <v>46252</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="14">
         <v>420</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="14">
         <v>60</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="14">
         <v>90</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="14">
         <v>75</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="14">
         <v>300</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="14">
         <v>6</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="14">
         <v>90</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="7">
         <f>SUM(B5:F5,H5)</f>
         <v>1035</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="7">
         <f>1440-I5</f>
         <v>405</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="M5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="N5" s="14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="13" customFormat="1">
-      <c r="A6" s="8">
+    <row r="6" spans="1:14" s="5" customFormat="1">
+      <c r="A6" s="11">
         <v>46253</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="14">
         <v>360</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="14">
         <v>40</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="14">
         <v>80</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="14">
         <v>90</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="14">
         <v>400</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="14">
         <v>7</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="14">
         <v>120</v>
       </c>
-      <c r="I6" s="9">
-        <f t="shared" ref="I6:I11" si="0">SUM(B6:F6,H6)</f>
+      <c r="I6" s="7">
+        <f t="shared" ref="I6:I12" si="0">SUM(B6:F6,H6)</f>
         <v>1090</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="7">
         <f>1440-I6</f>
         <v>350</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="M6" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="10" t="s">
+      <c r="N6" s="15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="14" customFormat="1">
-      <c r="A7" s="8">
+    <row r="7" spans="1:14" s="6" customFormat="1">
+      <c r="A7" s="11">
         <v>46254</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="13">
         <v>390</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="13">
         <v>55</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="13">
         <v>75</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="13">
         <v>60</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="13">
         <v>450</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="13">
         <v>8</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="13">
         <v>100</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="7">
         <f t="shared" si="0"/>
         <v>1130</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="7">
         <f>1440-I7</f>
         <v>310</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="14" customFormat="1">
-      <c r="A8" s="15">
+    <row r="8" spans="1:14" s="6" customFormat="1">
+      <c r="A8" s="12">
         <v>46255</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="13">
         <v>400</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="13">
         <v>60</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="13">
         <v>100</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="13">
         <v>55</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="13">
         <v>350</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="13">
         <v>7</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="13">
         <v>150</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="7">
         <f t="shared" si="0"/>
         <v>1115</v>
       </c>
-      <c r="J8" s="9">
-        <f t="shared" ref="J8:J11" si="1">1440-I8</f>
+      <c r="J8" s="7">
+        <f t="shared" ref="J8:J12" si="1">1440-I8</f>
         <v>325</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="M8" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="16" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="14" customFormat="1">
-      <c r="A9" s="15">
+    <row r="9" spans="1:14" s="6" customFormat="1">
+      <c r="A9" s="12">
         <v>46256</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="13">
         <v>480</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="13">
         <v>40</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="13">
         <v>85</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="13">
         <v>80</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="13">
         <v>0</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="13">
         <v>0</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="13">
         <v>170</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="7">
         <f t="shared" si="0"/>
         <v>855</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="7">
         <f t="shared" si="1"/>
         <v>585</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="M9" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="14" customFormat="1">
-      <c r="A10" s="15">
+    <row r="10" spans="1:14" s="6" customFormat="1">
+      <c r="A10" s="12">
         <v>46257</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="13">
         <v>450</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="13">
         <v>50</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="13">
         <v>150</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="13">
         <v>150</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="13">
         <v>0</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="13">
         <v>0</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="13">
         <v>250</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="7">
         <f t="shared" si="0"/>
         <v>1050</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="7">
         <f t="shared" si="1"/>
         <v>390</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="N10" s="7" t="s">
+      <c r="N10" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:14" s="14" customFormat="1">
-      <c r="A11" s="15">
+    <row r="11" spans="1:14" s="6" customFormat="1">
+      <c r="A11" s="12">
         <v>46258</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="13">
         <v>400</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="13">
         <v>55</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="13">
         <v>175</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="13">
         <v>80</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="13">
         <v>200</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="13">
         <v>4</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="13">
         <v>200</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="8">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="8">
         <f t="shared" si="1"/>
         <v>330</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="M11" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="N11" s="7" t="s">
+      <c r="N11" s="16" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="14" customFormat="1">
-      <c r="A12" s="15">
+    <row r="12" spans="1:14" s="6" customFormat="1">
+      <c r="A12" s="12">
         <v>46259</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="7"/>
-    </row>
-    <row r="13" spans="1:14" s="14" customFormat="1">
-      <c r="A13" s="15">
+      <c r="B12" s="13">
+        <v>320</v>
+      </c>
+      <c r="C12" s="13">
+        <v>80</v>
+      </c>
+      <c r="D12" s="13">
+        <v>90</v>
+      </c>
+      <c r="E12" s="13">
+        <v>120</v>
+      </c>
+      <c r="F12" s="13">
+        <v>300</v>
+      </c>
+      <c r="G12" s="13">
+        <v>5</v>
+      </c>
+      <c r="H12" s="13">
+        <v>190</v>
+      </c>
+      <c r="I12" s="8">
+        <f t="shared" si="0"/>
+        <v>1100</v>
+      </c>
+      <c r="J12" s="8">
+        <f t="shared" si="1"/>
+        <v>340</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="N12" s="16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="6" customFormat="1">
+      <c r="A13" s="12">
         <v>46260</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="7"/>
-    </row>
-    <row r="14" spans="1:14" s="14" customFormat="1">
-      <c r="A14" s="15">
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="16"/>
+    </row>
+    <row r="14" spans="1:14" s="6" customFormat="1">
+      <c r="A14" s="12">
         <v>46261</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="7"/>
-    </row>
-    <row r="15" spans="1:14" s="14" customFormat="1">
-      <c r="A15" s="15">
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="16"/>
+    </row>
+    <row r="15" spans="1:14" s="6" customFormat="1">
+      <c r="A15" s="12">
         <v>46262</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="7"/>
-    </row>
-    <row r="16" spans="1:14" s="14" customFormat="1">
-      <c r="A16" s="15">
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="16"/>
+    </row>
+    <row r="16" spans="1:14" s="6" customFormat="1">
+      <c r="A16" s="12">
         <v>46263</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="7"/>
-    </row>
-    <row r="17" spans="1:14" s="14" customFormat="1">
-      <c r="A17" s="15">
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="16"/>
+    </row>
+    <row r="17" spans="1:14" s="6" customFormat="1">
+      <c r="A17" s="12">
         <v>46264</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="7"/>
-    </row>
-    <row r="18" spans="1:14" s="14" customFormat="1">
-      <c r="A18" s="15">
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="16"/>
+    </row>
+    <row r="18" spans="1:14" s="6" customFormat="1">
+      <c r="A18" s="12">
         <v>46265</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="7"/>
-    </row>
-    <row r="19" spans="1:14" s="14" customFormat="1">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="7"/>
-    </row>
-    <row r="20" spans="1:14" s="14" customFormat="1">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="7"/>
-    </row>
-    <row r="21" spans="1:14" s="14" customFormat="1">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="7"/>
-    </row>
-    <row r="22" spans="1:14" s="14" customFormat="1">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="7"/>
-    </row>
-    <row r="23" spans="1:14" s="14" customFormat="1">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="7"/>
-    </row>
-    <row r="24" spans="1:14" s="14" customFormat="1">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="7"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="16"/>
+    </row>
+    <row r="19" spans="1:14" s="6" customFormat="1">
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="16"/>
+    </row>
+    <row r="20" spans="1:14" s="6" customFormat="1">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="16"/>
+    </row>
+    <row r="21" spans="1:14" s="6" customFormat="1">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="16"/>
+    </row>
+    <row r="22" spans="1:14" s="6" customFormat="1">
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="16"/>
+    </row>
+    <row r="23" spans="1:14" s="6" customFormat="1">
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="16"/>
+    </row>
+    <row r="24" spans="1:14" s="6" customFormat="1">
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="16"/>
     </row>
   </sheetData>
   <dataValidations count="3">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>REGULAR WORKING DAY</t>
+  </si>
+  <si>
+    <t>FEELING HAPPY</t>
   </si>
 </sst>
 </file>
@@ -565,7 +568,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -739,7 +742,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="7">
-        <f t="shared" ref="I6:I12" si="0">SUM(B6:F6,H6)</f>
+        <f t="shared" ref="I6:I13" si="0">SUM(B6:F6,H6)</f>
         <v>1090</v>
       </c>
       <c r="J6" s="7">
@@ -835,7 +838,7 @@
         <v>1115</v>
       </c>
       <c r="J8" s="7">
-        <f t="shared" ref="J8:J12" si="1">1440-I8</f>
+        <f t="shared" ref="J8:J13" si="1">1440-I8</f>
         <v>325</v>
       </c>
       <c r="K8" s="13" t="s">
@@ -1039,19 +1042,47 @@
       <c r="A13" s="12">
         <v>46260</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="16"/>
+      <c r="B13" s="13">
+        <v>470</v>
+      </c>
+      <c r="C13" s="13">
+        <v>50</v>
+      </c>
+      <c r="D13" s="13">
+        <v>170</v>
+      </c>
+      <c r="E13" s="13">
+        <v>80</v>
+      </c>
+      <c r="F13" s="13">
+        <v>0</v>
+      </c>
+      <c r="G13" s="13">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13">
+        <v>200</v>
+      </c>
+      <c r="I13" s="8">
+        <f t="shared" si="0"/>
+        <v>970</v>
+      </c>
+      <c r="J13" s="8">
+        <f t="shared" si="1"/>
+        <v>470</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M13" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="N13" s="16" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="14" spans="1:14" s="6" customFormat="1">
       <c r="A14" s="12">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="38">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -136,6 +136,12 @@
   </si>
   <si>
     <t>FEELING HAPPY</t>
+  </si>
+  <si>
+    <t>WENT TO MARKET</t>
+  </si>
+  <si>
+    <t>ENJOYED RAKSHABANDHAN</t>
   </si>
 </sst>
 </file>
@@ -568,7 +574,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -742,7 +748,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="7">
-        <f t="shared" ref="I6:I13" si="0">SUM(B6:F6,H6)</f>
+        <f t="shared" ref="I6:I15" si="0">SUM(B6:F6,H6)</f>
         <v>1090</v>
       </c>
       <c r="J6" s="7">
@@ -838,7 +844,7 @@
         <v>1115</v>
       </c>
       <c r="J8" s="7">
-        <f t="shared" ref="J8:J13" si="1">1440-I8</f>
+        <f t="shared" ref="J8:J15" si="1">1440-I8</f>
         <v>325</v>
       </c>
       <c r="K8" s="13" t="s">
@@ -1088,37 +1094,93 @@
       <c r="A14" s="12">
         <v>46261</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="16"/>
+      <c r="B14" s="13">
+        <v>320</v>
+      </c>
+      <c r="C14" s="13">
+        <v>45</v>
+      </c>
+      <c r="D14" s="13">
+        <v>95</v>
+      </c>
+      <c r="E14" s="13">
+        <v>70</v>
+      </c>
+      <c r="F14" s="13">
+        <v>400</v>
+      </c>
+      <c r="G14" s="13">
+        <v>6</v>
+      </c>
+      <c r="H14" s="13">
+        <v>160</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="0"/>
+        <v>1090</v>
+      </c>
+      <c r="J14" s="8">
+        <f t="shared" si="1"/>
+        <v>350</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="M14" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" s="16" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="15" spans="1:14" s="6" customFormat="1">
       <c r="A15" s="12">
         <v>46262</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="16"/>
+      <c r="B15" s="13">
+        <v>300</v>
+      </c>
+      <c r="C15" s="13">
+        <v>65</v>
+      </c>
+      <c r="D15" s="13">
+        <v>70</v>
+      </c>
+      <c r="E15" s="13">
+        <v>65</v>
+      </c>
+      <c r="F15" s="13">
+        <v>200</v>
+      </c>
+      <c r="G15" s="13">
+        <v>3</v>
+      </c>
+      <c r="H15" s="13">
+        <v>200</v>
+      </c>
+      <c r="I15" s="8">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="J15" s="8">
+        <f t="shared" si="1"/>
+        <v>540</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="M15" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="N15" s="16" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="16" spans="1:14" s="6" customFormat="1">
       <c r="A16" s="12">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -1,17 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07a2f6804baade4d/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_CD29518021CD0CB7BEF766B3602171D3BF86047C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20C60B92-711B-447E-8DA8-599F334D45DA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DAILY LOG" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -28,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="41">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -142,13 +148,22 @@
   </si>
   <si>
     <t>ENJOYED RAKSHABANDHAN</t>
+  </si>
+  <si>
+    <t>STRESSED</t>
+  </si>
+  <si>
+    <t>FOCUSED ON CODING</t>
+  </si>
+  <si>
+    <t>WENT FOR OUTING</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -207,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -225,12 +240,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -255,7 +264,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -574,16 +583,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" customWidth="1"/>
     <col min="2" max="11" width="14.77734375" customWidth="1"/>
@@ -592,47 +601,47 @@
     <col min="14" max="14" width="31.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="17" customFormat="1" ht="13.8">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:14" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="10"/>
-    </row>
-    <row r="2" spans="1:14" s="17" customFormat="1" ht="13.8">
-      <c r="A2" s="9" t="s">
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="8"/>
+    </row>
+    <row r="2" spans="1:14" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="10"/>
-    </row>
-    <row r="4" spans="1:14" s="4" customFormat="1" ht="52.2">
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="8"/>
+    </row>
+    <row r="4" spans="1:14" s="4" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
@@ -676,671 +685,713 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="5" customFormat="1">
-      <c r="A5" s="11">
+    <row r="5" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
         <v>46252</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="12">
         <v>420</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="12">
         <v>60</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="12">
         <v>90</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="12">
         <v>75</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="12">
         <v>300</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="12">
         <v>6</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="12">
         <v>90</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="5">
         <f>SUM(B5:F5,H5)</f>
         <v>1035</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="5">
         <f>1440-I5</f>
         <v>405</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="K5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="L5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="14" t="s">
+      <c r="M5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="N5" s="14" t="s">
+      <c r="N5" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="5" customFormat="1">
-      <c r="A6" s="11">
+    <row r="6" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
         <v>46253</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="12">
         <v>360</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="12">
         <v>40</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="12">
         <v>80</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="12">
         <v>90</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="12">
         <v>400</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="12">
         <v>7</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="12">
         <v>120</v>
       </c>
-      <c r="I6" s="7">
-        <f t="shared" ref="I6:I15" si="0">SUM(B6:F6,H6)</f>
+      <c r="I6" s="5">
+        <f t="shared" ref="I6:I17" si="0">SUM(B6:F6,H6)</f>
         <v>1090</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="5">
         <f>1440-I6</f>
         <v>350</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="14" t="s">
+      <c r="L6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="M6" s="14" t="s">
+      <c r="M6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="15" t="s">
+      <c r="N6" s="13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="6" customFormat="1">
-      <c r="A7" s="11">
+    <row r="7" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
         <v>46254</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="11">
         <v>390</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="11">
         <v>55</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="11">
         <v>75</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="11">
         <v>60</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="11">
         <v>450</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="11">
         <v>8</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="11">
         <v>100</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="5">
         <f t="shared" si="0"/>
         <v>1130</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="5">
         <f>1440-I7</f>
         <v>310</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="L7" s="13" t="s">
+      <c r="L7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="M7" s="13" t="s">
+      <c r="M7" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="N7" s="16" t="s">
+      <c r="N7" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="6" customFormat="1">
-      <c r="A8" s="12">
+    <row r="8" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10">
         <v>46255</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="11">
         <v>400</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="11">
         <v>60</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="11">
         <v>100</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="11">
         <v>55</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="11">
         <v>350</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="11">
         <v>7</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="11">
         <v>150</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="5">
         <f t="shared" si="0"/>
         <v>1115</v>
       </c>
-      <c r="J8" s="7">
-        <f t="shared" ref="J8:J15" si="1">1440-I8</f>
+      <c r="J8" s="5">
+        <f t="shared" ref="J8:J17" si="1">1440-I8</f>
         <v>325</v>
       </c>
-      <c r="K8" s="13" t="s">
+      <c r="K8" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="L8" s="13" t="s">
+      <c r="L8" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="M8" s="13" t="s">
+      <c r="M8" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="N8" s="16" t="s">
+      <c r="N8" s="14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="6" customFormat="1">
-      <c r="A9" s="12">
+    <row r="9" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="10">
         <v>46256</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="11">
         <v>480</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="11">
         <v>40</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="11">
         <v>85</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="11">
         <v>80</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="11">
         <v>0</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="11">
         <v>0</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="11">
         <v>170</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="5">
         <f t="shared" si="0"/>
         <v>855</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="5">
         <f t="shared" si="1"/>
         <v>585</v>
       </c>
-      <c r="K9" s="13" t="s">
+      <c r="K9" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L9" s="13" t="s">
+      <c r="L9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="M9" s="13" t="s">
+      <c r="M9" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="N9" s="16" t="s">
+      <c r="N9" s="14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="6" customFormat="1">
-      <c r="A10" s="12">
+    <row r="10" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10">
         <v>46257</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="11">
         <v>450</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="11">
         <v>50</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="11">
         <v>150</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="11">
         <v>150</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="11">
         <v>0</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="11">
         <v>0</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="11">
         <v>250</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="5">
         <f t="shared" si="0"/>
         <v>1050</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="5">
         <f t="shared" si="1"/>
         <v>390</v>
       </c>
-      <c r="K10" s="13" t="s">
+      <c r="K10" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="13" t="s">
+      <c r="L10" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="M10" s="13" t="s">
+      <c r="M10" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="N10" s="16" t="s">
+      <c r="N10" s="14" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:14" s="6" customFormat="1">
-      <c r="A11" s="12">
+    <row r="11" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10">
         <v>46258</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="11">
         <v>400</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="11">
         <v>55</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="11">
         <v>175</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="11">
         <v>80</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="11">
         <v>200</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="11">
         <v>4</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="11">
         <v>200</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="6">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="6">
         <f t="shared" si="1"/>
         <v>330</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="L11" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="M11" s="13" t="s">
+      <c r="M11" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="N11" s="16" t="s">
+      <c r="N11" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="6" customFormat="1">
-      <c r="A12" s="12">
+    <row r="12" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="10">
         <v>46259</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="11">
         <v>320</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="11">
         <v>80</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="11">
         <v>90</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="11">
         <v>120</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="11">
         <v>300</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="11">
         <v>5</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="11">
         <v>190</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="6">
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="6">
         <f t="shared" si="1"/>
         <v>340</v>
       </c>
-      <c r="K12" s="13" t="s">
+      <c r="K12" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L12" s="13" t="s">
+      <c r="L12" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="M12" s="13" t="s">
+      <c r="M12" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="N12" s="16" t="s">
+      <c r="N12" s="14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:14" s="6" customFormat="1">
-      <c r="A13" s="12">
+    <row r="13" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="10">
         <v>46260</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="11">
         <v>470</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="11">
         <v>50</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="11">
         <v>170</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="11">
         <v>80</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="11">
         <v>0</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="11">
         <v>0</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="11">
         <v>200</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="6">
         <f t="shared" si="0"/>
         <v>970</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="6">
         <f t="shared" si="1"/>
         <v>470</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="K13" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="L13" s="13" t="s">
+      <c r="L13" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="M13" s="13" t="s">
+      <c r="M13" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="N13" s="16" t="s">
+      <c r="N13" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:14" s="6" customFormat="1">
-      <c r="A14" s="12">
+    <row r="14" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="10">
         <v>46261</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="11">
         <v>320</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="11">
         <v>45</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="11">
         <v>95</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="11">
         <v>70</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="11">
         <v>400</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="11">
         <v>6</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="11">
         <v>160</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="6">
         <f t="shared" si="0"/>
         <v>1090</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="6">
         <f t="shared" si="1"/>
         <v>350</v>
       </c>
-      <c r="K14" s="13" t="s">
+      <c r="K14" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="L14" s="13" t="s">
+      <c r="L14" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="M14" s="13" t="s">
+      <c r="M14" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="N14" s="16" t="s">
+      <c r="N14" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:14" s="6" customFormat="1">
-      <c r="A15" s="12">
+    <row r="15" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10">
         <v>46262</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="11">
         <v>300</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="11">
         <v>65</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="11">
         <v>70</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="11">
         <v>65</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="11">
         <v>200</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="11">
         <v>3</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="11">
         <v>200</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="6">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="6">
         <f t="shared" si="1"/>
         <v>540</v>
       </c>
-      <c r="K15" s="13" t="s">
+      <c r="K15" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="L15" s="13" t="s">
+      <c r="L15" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="M15" s="13" t="s">
+      <c r="M15" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="16" t="s">
+      <c r="N15" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:14" s="6" customFormat="1">
-      <c r="A16" s="12">
+    <row r="16" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="10">
         <v>46263</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="16"/>
-    </row>
-    <row r="17" spans="1:14" s="6" customFormat="1">
-      <c r="A17" s="12">
+      <c r="B16" s="11">
+        <v>380</v>
+      </c>
+      <c r="C16" s="11">
+        <v>40</v>
+      </c>
+      <c r="D16" s="11">
+        <v>100</v>
+      </c>
+      <c r="E16" s="11">
+        <v>110</v>
+      </c>
+      <c r="F16" s="11">
+        <v>0</v>
+      </c>
+      <c r="G16" s="11">
+        <v>0</v>
+      </c>
+      <c r="H16" s="11">
+        <v>185</v>
+      </c>
+      <c r="I16" s="6">
+        <f t="shared" si="0"/>
+        <v>815</v>
+      </c>
+      <c r="J16" s="6">
+        <f t="shared" si="1"/>
+        <v>625</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N16" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="10">
         <v>46264</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="16"/>
-    </row>
-    <row r="18" spans="1:14" s="6" customFormat="1">
-      <c r="A18" s="12">
+      <c r="B17" s="11">
+        <v>420</v>
+      </c>
+      <c r="C17" s="11">
+        <v>55</v>
+      </c>
+      <c r="D17" s="11">
+        <v>120</v>
+      </c>
+      <c r="E17" s="11">
+        <v>100</v>
+      </c>
+      <c r="F17" s="11">
+        <v>0</v>
+      </c>
+      <c r="G17" s="11">
+        <v>0</v>
+      </c>
+      <c r="H17" s="11">
+        <v>180</v>
+      </c>
+      <c r="I17" s="6">
+        <f t="shared" si="0"/>
+        <v>875</v>
+      </c>
+      <c r="J17" s="6">
+        <f t="shared" si="1"/>
+        <v>565</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N17" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="10">
         <v>46265</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="16"/>
-    </row>
-    <row r="19" spans="1:14" s="6" customFormat="1">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="16"/>
-    </row>
-    <row r="20" spans="1:14" s="6" customFormat="1">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="16"/>
-    </row>
-    <row r="21" spans="1:14" s="6" customFormat="1">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="16"/>
-    </row>
-    <row r="22" spans="1:14" s="6" customFormat="1">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="16"/>
-    </row>
-    <row r="23" spans="1:14" s="6" customFormat="1">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="16"/>
-    </row>
-    <row r="24" spans="1:14" s="6" customFormat="1">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="16"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="14"/>
+    </row>
+    <row r="19" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="14"/>
+    </row>
+    <row r="20" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="14"/>
+    </row>
+    <row r="21" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="14"/>
+    </row>
+    <row r="22" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="14"/>
+    </row>
+    <row r="23" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="14"/>
+    </row>
+    <row r="24" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="14"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K24" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"EXCELLENT,GOOD,NEUTRAL,LOW,STRESSED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L24" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"VERY SATISFIED,SATISFIED,NEUTRAL,UNSATISFIED,VERY UNSATISFIED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5:M24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5:M24" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"HIGH,MEDIUM,LOW"</formula1>
     </dataValidation>
   </dataValidations>

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -1,23 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07a2f6804baade4d/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_CD29518021CD0CB7BEF766B3602171D3BF86047C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20C60B92-711B-447E-8DA8-599F334D45DA}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
     <sheet name="DAILY LOG" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="124519"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="42">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -157,13 +151,16 @@
   </si>
   <si>
     <t>WENT FOR OUTING</t>
+  </si>
+  <si>
+    <t>BACK TO NORMAL ROUTINE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -583,16 +580,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.77734375" customWidth="1"/>
     <col min="2" max="11" width="14.77734375" customWidth="1"/>
@@ -601,7 +598,7 @@
     <col min="14" max="14" width="31.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="15" customFormat="1" ht="13.8">
       <c r="A1" s="7" t="s">
         <v>14</v>
       </c>
@@ -621,7 +618,7 @@
       <c r="M1" s="7"/>
       <c r="N1" s="8"/>
     </row>
-    <row r="2" spans="1:14" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" s="15" customFormat="1" ht="13.8">
       <c r="A2" s="7" t="s">
         <v>13</v>
       </c>
@@ -641,7 +638,7 @@
       <c r="M2" s="7"/>
       <c r="N2" s="8"/>
     </row>
-    <row r="4" spans="1:14" s="4" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" s="4" customFormat="1" ht="52.2">
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
@@ -685,7 +682,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" s="5" customFormat="1">
       <c r="A5" s="9">
         <v>46252</v>
       </c>
@@ -731,7 +728,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" s="5" customFormat="1">
       <c r="A6" s="9">
         <v>46253</v>
       </c>
@@ -757,7 +754,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="5">
-        <f t="shared" ref="I6:I17" si="0">SUM(B6:F6,H6)</f>
+        <f t="shared" ref="I6:I18" si="0">SUM(B6:F6,H6)</f>
         <v>1090</v>
       </c>
       <c r="J6" s="5">
@@ -777,7 +774,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" s="6" customFormat="1">
       <c r="A7" s="9">
         <v>46254</v>
       </c>
@@ -823,7 +820,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" s="6" customFormat="1">
       <c r="A8" s="10">
         <v>46255</v>
       </c>
@@ -853,7 +850,7 @@
         <v>1115</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" ref="J8:J17" si="1">1440-I8</f>
+        <f t="shared" ref="J8:J18" si="1">1440-I8</f>
         <v>325</v>
       </c>
       <c r="K8" s="11" t="s">
@@ -869,7 +866,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" s="6" customFormat="1">
       <c r="A9" s="10">
         <v>46256</v>
       </c>
@@ -915,7 +912,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" s="6" customFormat="1">
       <c r="A10" s="10">
         <v>46257</v>
       </c>
@@ -961,7 +958,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" s="6" customFormat="1">
       <c r="A11" s="10">
         <v>46258</v>
       </c>
@@ -1007,7 +1004,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" s="6" customFormat="1">
       <c r="A12" s="10">
         <v>46259</v>
       </c>
@@ -1053,7 +1050,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" s="6" customFormat="1">
       <c r="A13" s="10">
         <v>46260</v>
       </c>
@@ -1099,7 +1096,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" s="6" customFormat="1">
       <c r="A14" s="10">
         <v>46261</v>
       </c>
@@ -1145,7 +1142,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" s="6" customFormat="1">
       <c r="A15" s="10">
         <v>46262</v>
       </c>
@@ -1191,7 +1188,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" s="6" customFormat="1">
       <c r="A16" s="10">
         <v>46263</v>
       </c>
@@ -1237,7 +1234,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" s="6" customFormat="1">
       <c r="A17" s="10">
         <v>46264</v>
       </c>
@@ -1283,23 +1280,53 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" s="6" customFormat="1">
       <c r="A18" s="10">
         <v>46265</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="14"/>
-    </row>
-    <row r="19" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="11">
+        <v>430</v>
+      </c>
+      <c r="C18" s="11">
+        <v>65</v>
+      </c>
+      <c r="D18" s="11">
+        <v>90</v>
+      </c>
+      <c r="E18" s="11">
+        <v>105</v>
+      </c>
+      <c r="F18" s="11">
+        <v>200</v>
+      </c>
+      <c r="G18" s="11">
+        <v>4</v>
+      </c>
+      <c r="H18" s="11">
+        <v>190</v>
+      </c>
+      <c r="I18" s="6">
+        <f t="shared" si="0"/>
+        <v>1080</v>
+      </c>
+      <c r="J18" s="6">
+        <f t="shared" si="1"/>
+        <v>360</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" s="6" customFormat="1">
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -1313,7 +1340,7 @@
       <c r="M19" s="11"/>
       <c r="N19" s="14"/>
     </row>
-    <row r="20" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" s="6" customFormat="1">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -1327,7 +1354,7 @@
       <c r="M20" s="11"/>
       <c r="N20" s="14"/>
     </row>
-    <row r="21" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" s="6" customFormat="1">
       <c r="A21" s="11"/>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -1341,7 +1368,7 @@
       <c r="M21" s="11"/>
       <c r="N21" s="14"/>
     </row>
-    <row r="22" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" s="6" customFormat="1">
       <c r="A22" s="11"/>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -1355,7 +1382,7 @@
       <c r="M22" s="11"/>
       <c r="N22" s="14"/>
     </row>
-    <row r="23" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" s="6" customFormat="1">
       <c r="A23" s="11"/>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -1369,7 +1396,7 @@
       <c r="M23" s="11"/>
       <c r="N23" s="14"/>
     </row>
-    <row r="24" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" s="6" customFormat="1">
       <c r="A24" s="11"/>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -1385,13 +1412,13 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K24" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K24">
       <formula1>"EXCELLENT,GOOD,NEUTRAL,LOW,STRESSED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L24" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L24">
       <formula1>"VERY SATISFIED,SATISFIED,NEUTRAL,UNSATISFIED,VERY UNSATISFIED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5:M24" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5:M24">
       <formula1>"HIGH,MEDIUM,LOW"</formula1>
     </dataValidation>
   </dataValidations>

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="43">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t>BACK TO NORMAL ROUTINE</t>
+  </si>
+  <si>
+    <t>NEW MONTH , BACK TO ROUTINE</t>
   </si>
 </sst>
 </file>
@@ -580,7 +583,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -754,7 +757,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="5">
-        <f t="shared" ref="I6:I18" si="0">SUM(B6:F6,H6)</f>
+        <f t="shared" ref="I6:I19" si="0">SUM(B6:F6,H6)</f>
         <v>1090</v>
       </c>
       <c r="J6" s="5">
@@ -850,7 +853,7 @@
         <v>1115</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" ref="J8:J18" si="1">1440-I8</f>
+        <f t="shared" ref="J8:J19" si="1">1440-I8</f>
         <v>325</v>
       </c>
       <c r="K8" s="11" t="s">
@@ -1327,18 +1330,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" s="6" customFormat="1">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="14"/>
+      <c r="A19" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B19" s="11">
+        <v>300</v>
+      </c>
+      <c r="C19" s="11">
+        <v>60</v>
+      </c>
+      <c r="D19" s="11">
+        <v>95</v>
+      </c>
+      <c r="E19" s="11">
+        <v>95</v>
+      </c>
+      <c r="F19" s="11">
+        <v>300</v>
+      </c>
+      <c r="G19" s="11">
+        <v>5</v>
+      </c>
+      <c r="H19" s="11">
+        <v>180</v>
+      </c>
+      <c r="I19" s="6">
+        <f t="shared" si="0"/>
+        <v>1030</v>
+      </c>
+      <c r="J19" s="6">
+        <f t="shared" si="1"/>
+        <v>410</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N19" s="14" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="20" spans="1:14" s="6" customFormat="1">
       <c r="A20" s="11"/>

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="45">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -157,6 +157,12 @@
   </si>
   <si>
     <t>NEW MONTH , BACK TO ROUTINE</t>
+  </si>
+  <si>
+    <t>PRODUCTIVE DAY</t>
+  </si>
+  <si>
+    <t>FELT UNWELL</t>
   </si>
 </sst>
 </file>
@@ -583,7 +589,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -757,7 +763,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="5">
-        <f t="shared" ref="I6:I19" si="0">SUM(B6:F6,H6)</f>
+        <f t="shared" ref="I6:I21" si="0">SUM(B6:F6,H6)</f>
         <v>1090</v>
       </c>
       <c r="J6" s="5">
@@ -853,7 +859,7 @@
         <v>1115</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" ref="J8:J19" si="1">1440-I8</f>
+        <f t="shared" ref="J8:J21" si="1">1440-I8</f>
         <v>325</v>
       </c>
       <c r="K8" s="11" t="s">
@@ -1376,35 +1382,101 @@
       </c>
     </row>
     <row r="20" spans="1:14" s="6" customFormat="1">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="14"/>
+      <c r="A20" s="10">
+        <v>46267</v>
+      </c>
+      <c r="B20" s="11">
+        <v>480</v>
+      </c>
+      <c r="C20" s="11">
+        <v>40</v>
+      </c>
+      <c r="D20" s="11">
+        <v>105</v>
+      </c>
+      <c r="E20" s="11">
+        <v>75</v>
+      </c>
+      <c r="F20" s="11">
+        <v>250</v>
+      </c>
+      <c r="G20" s="11">
+        <v>5</v>
+      </c>
+      <c r="H20" s="11">
+        <v>175</v>
+      </c>
+      <c r="I20" s="6">
+        <f t="shared" si="0"/>
+        <v>1125</v>
+      </c>
+      <c r="J20" s="6">
+        <f t="shared" si="1"/>
+        <v>315</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" s="14" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="21" spans="1:14" s="6" customFormat="1">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="14"/>
+      <c r="A21" s="10">
+        <v>46268</v>
+      </c>
+      <c r="B21" s="11">
+        <v>330</v>
+      </c>
+      <c r="C21" s="11">
+        <v>65</v>
+      </c>
+      <c r="D21" s="11">
+        <v>75</v>
+      </c>
+      <c r="E21" s="11">
+        <v>95</v>
+      </c>
+      <c r="F21" s="11">
+        <v>300</v>
+      </c>
+      <c r="G21" s="11">
+        <v>6</v>
+      </c>
+      <c r="H21" s="11">
+        <v>165</v>
+      </c>
+      <c r="I21" s="6">
+        <f t="shared" si="0"/>
+        <v>1030</v>
+      </c>
+      <c r="J21" s="6">
+        <f t="shared" si="1"/>
+        <v>410</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N21" s="14" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="22" spans="1:14" s="6" customFormat="1">
-      <c r="A22" s="11"/>
+      <c r="A22" s="10">
+        <v>46269</v>
+      </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="47">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -163,6 +163,12 @@
   </si>
   <si>
     <t>FELT UNWELL</t>
+  </si>
+  <si>
+    <t>GREAT ENERGY BOOST</t>
+  </si>
+  <si>
+    <t>NEEDED SOME REST</t>
   </si>
 </sst>
 </file>
@@ -589,7 +595,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -763,7 +769,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="5">
-        <f t="shared" ref="I6:I21" si="0">SUM(B6:F6,H6)</f>
+        <f t="shared" ref="I6:I23" si="0">SUM(B6:F6,H6)</f>
         <v>1090</v>
       </c>
       <c r="J6" s="5">
@@ -859,7 +865,7 @@
         <v>1115</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" ref="J8:J21" si="1">1440-I8</f>
+        <f t="shared" ref="J8:J23" si="1">1440-I8</f>
         <v>325</v>
       </c>
       <c r="K8" s="11" t="s">
@@ -1477,31 +1483,93 @@
       <c r="A22" s="10">
         <v>46269</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="14"/>
+      <c r="B22" s="11">
+        <v>370</v>
+      </c>
+      <c r="C22" s="11">
+        <v>75</v>
+      </c>
+      <c r="D22" s="11">
+        <v>85</v>
+      </c>
+      <c r="E22" s="11">
+        <v>80</v>
+      </c>
+      <c r="F22" s="11">
+        <v>350</v>
+      </c>
+      <c r="G22" s="11">
+        <v>7</v>
+      </c>
+      <c r="H22" s="11">
+        <v>185</v>
+      </c>
+      <c r="I22" s="6">
+        <f t="shared" si="0"/>
+        <v>1145</v>
+      </c>
+      <c r="J22" s="6">
+        <f t="shared" si="1"/>
+        <v>295</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N22" s="14" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="23" spans="1:14" s="6" customFormat="1">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="14"/>
+      <c r="A23" s="10">
+        <v>46270</v>
+      </c>
+      <c r="B23" s="11">
+        <v>450</v>
+      </c>
+      <c r="C23" s="11">
+        <v>60</v>
+      </c>
+      <c r="D23" s="11">
+        <v>100</v>
+      </c>
+      <c r="E23" s="11">
+        <v>100</v>
+      </c>
+      <c r="F23" s="11">
+        <v>50</v>
+      </c>
+      <c r="G23" s="11">
+        <v>1</v>
+      </c>
+      <c r="H23" s="11">
+        <v>195</v>
+      </c>
+      <c r="I23" s="6">
+        <f t="shared" si="0"/>
+        <v>955</v>
+      </c>
+      <c r="J23" s="6">
+        <f t="shared" si="1"/>
+        <v>485</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N23" s="14" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="24" spans="1:14" s="6" customFormat="1">
       <c r="A24" s="11"/>

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -1,17 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEF32043-02DF-4734-955C-676B2D85F88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DAILY LOG" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -21,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -28,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="49">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -169,13 +177,19 @@
   </si>
   <si>
     <t>NEEDED SOME REST</t>
+  </si>
+  <si>
+    <t>PREPARED FOR CA</t>
+  </si>
+  <si>
+    <t>APPEARED FOR FIRST CA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,18 +306,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
-<file path=xl/persons/person0.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
-<file path=xl/persons/person1.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -595,16 +597,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N48"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" customWidth="1"/>
     <col min="2" max="11" width="14.77734375" customWidth="1"/>
@@ -613,7 +615,7 @@
     <col min="14" max="14" width="31.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="15" customFormat="1" ht="13.8">
+    <row r="1" spans="1:14" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>14</v>
       </c>
@@ -633,7 +635,7 @@
       <c r="M1" s="7"/>
       <c r="N1" s="8"/>
     </row>
-    <row r="2" spans="1:14" s="15" customFormat="1" ht="13.8">
+    <row r="2" spans="1:14" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>13</v>
       </c>
@@ -653,7 +655,7 @@
       <c r="M2" s="7"/>
       <c r="N2" s="8"/>
     </row>
-    <row r="4" spans="1:14" s="4" customFormat="1" ht="52.2">
+    <row r="4" spans="1:14" s="4" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
@@ -697,7 +699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="5" customFormat="1">
+    <row r="5" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>46252</v>
       </c>
@@ -743,7 +745,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="5" customFormat="1">
+    <row r="6" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>46253</v>
       </c>
@@ -769,7 +771,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="5">
-        <f t="shared" ref="I6:I23" si="0">SUM(B6:F6,H6)</f>
+        <f t="shared" ref="I6:I25" si="0">SUM(B6:F6,H6)</f>
         <v>1090</v>
       </c>
       <c r="J6" s="5">
@@ -789,7 +791,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="6" customFormat="1">
+    <row r="7" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>46254</v>
       </c>
@@ -835,7 +837,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="6" customFormat="1">
+    <row r="8" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>46255</v>
       </c>
@@ -865,7 +867,7 @@
         <v>1115</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" ref="J8:J23" si="1">1440-I8</f>
+        <f t="shared" ref="J8:J25" si="1">1440-I8</f>
         <v>325</v>
       </c>
       <c r="K8" s="11" t="s">
@@ -881,7 +883,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="6" customFormat="1">
+    <row r="9" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
         <v>46256</v>
       </c>
@@ -927,7 +929,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="6" customFormat="1">
+    <row r="10" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>46257</v>
       </c>
@@ -973,7 +975,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:14" s="6" customFormat="1">
+    <row r="11" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <v>46258</v>
       </c>
@@ -1019,7 +1021,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="6" customFormat="1">
+    <row r="12" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>46259</v>
       </c>
@@ -1065,7 +1067,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:14" s="6" customFormat="1">
+    <row r="13" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <v>46260</v>
       </c>
@@ -1111,7 +1113,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:14" s="6" customFormat="1">
+    <row r="14" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>46261</v>
       </c>
@@ -1157,7 +1159,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:14" s="6" customFormat="1">
+    <row r="15" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
         <v>46262</v>
       </c>
@@ -1203,7 +1205,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:14" s="6" customFormat="1">
+    <row r="16" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>46263</v>
       </c>
@@ -1249,7 +1251,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:14" s="6" customFormat="1">
+    <row r="17" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
         <v>46264</v>
       </c>
@@ -1295,7 +1297,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:14" s="6" customFormat="1">
+    <row r="18" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>46265</v>
       </c>
@@ -1341,7 +1343,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:14" s="6" customFormat="1">
+    <row r="19" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
         <v>46266</v>
       </c>
@@ -1387,7 +1389,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:14" s="6" customFormat="1">
+    <row r="20" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>46267</v>
       </c>
@@ -1433,7 +1435,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:14" s="6" customFormat="1">
+    <row r="21" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
         <v>46268</v>
       </c>
@@ -1479,7 +1481,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:14" s="6" customFormat="1">
+    <row r="22" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>46269</v>
       </c>
@@ -1525,7 +1527,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:14" s="6" customFormat="1">
+    <row r="23" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
         <v>46270</v>
       </c>
@@ -1571,29 +1573,493 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:14" s="6" customFormat="1">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="14"/>
+    <row r="24" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="10">
+        <v>46271</v>
+      </c>
+      <c r="B24" s="11">
+        <v>350</v>
+      </c>
+      <c r="C24" s="11">
+        <v>55</v>
+      </c>
+      <c r="D24" s="11">
+        <v>200</v>
+      </c>
+      <c r="E24" s="11">
+        <v>90</v>
+      </c>
+      <c r="F24" s="11">
+        <v>0</v>
+      </c>
+      <c r="G24" s="11">
+        <v>0</v>
+      </c>
+      <c r="H24" s="11">
+        <v>180</v>
+      </c>
+      <c r="I24" s="6">
+        <f t="shared" si="0"/>
+        <v>875</v>
+      </c>
+      <c r="J24" s="6">
+        <f t="shared" si="1"/>
+        <v>565</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N24" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="10">
+        <v>46272</v>
+      </c>
+      <c r="B25" s="11">
+        <v>400</v>
+      </c>
+      <c r="C25" s="11">
+        <v>60</v>
+      </c>
+      <c r="D25" s="11">
+        <v>125</v>
+      </c>
+      <c r="E25" s="11">
+        <v>85</v>
+      </c>
+      <c r="F25" s="11">
+        <v>320</v>
+      </c>
+      <c r="G25" s="11">
+        <v>6</v>
+      </c>
+      <c r="H25" s="11">
+        <v>170</v>
+      </c>
+      <c r="I25" s="6">
+        <f t="shared" si="0"/>
+        <v>1160</v>
+      </c>
+      <c r="J25" s="6">
+        <f t="shared" si="1"/>
+        <v>280</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N25" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="14"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="10">
+        <v>46274</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="14"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="10">
+        <v>46275</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="14"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="10">
+        <v>46276</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="14"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="10">
+        <v>46277</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="14"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="10">
+        <v>46278</v>
+      </c>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="14"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="10">
+        <v>46279</v>
+      </c>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="14"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="14"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="10">
+        <v>46281</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="14"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="10">
+        <v>46282</v>
+      </c>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="14"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="10">
+        <v>46283</v>
+      </c>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="14"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="10">
+        <v>46284</v>
+      </c>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="14"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="10">
+        <v>46285</v>
+      </c>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="14"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="10">
+        <v>46286</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="14"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="14"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="10">
+        <v>46288</v>
+      </c>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="14"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="10">
+        <v>46289</v>
+      </c>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+      <c r="N42" s="14"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="10">
+        <v>46290</v>
+      </c>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="14"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" s="10">
+        <v>46291</v>
+      </c>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="14"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" s="10">
+        <v>46292</v>
+      </c>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+      <c r="N45" s="14"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" s="10">
+        <v>46293</v>
+      </c>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="14"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C47" s="6"/>
+      <c r="I47" s="6"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C48" s="6"/>
+      <c r="I48" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K46" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"EXCELLENT,GOOD,NEUTRAL,LOW,STRESSED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L46" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"VERY SATISFIED,SATISFIED,NEUTRAL,UNSATISFIED,VERY UNSATISFIED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5:M24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5:M46" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"HIGH,MEDIUM,LOW"</formula1>
     </dataValidation>
   </dataValidations>

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEF32043-02DF-4734-955C-676B2D85F88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CCF225-71F0-404A-9379-A58A0D86D324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="50">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -183,6 +183,9 @@
   </si>
   <si>
     <t>APPEARED FOR FIRST CA</t>
+  </si>
+  <si>
+    <t>FOCUSED ON STUDY</t>
   </si>
 </sst>
 </file>
@@ -771,7 +774,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="5">
-        <f t="shared" ref="I6:I25" si="0">SUM(B6:F6,H6)</f>
+        <f t="shared" ref="I6:I26" si="0">SUM(B6:F6,H6)</f>
         <v>1090</v>
       </c>
       <c r="J6" s="5">
@@ -867,7 +870,7 @@
         <v>1115</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" ref="J8:J25" si="1">1440-I8</f>
+        <f t="shared" ref="J8:J26" si="1">1440-I8</f>
         <v>325</v>
       </c>
       <c r="K8" s="11" t="s">
@@ -1669,19 +1672,47 @@
       <c r="A26" s="10">
         <v>46273</v>
       </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="14"/>
+      <c r="B26" s="11">
+        <v>280</v>
+      </c>
+      <c r="C26" s="11">
+        <v>70</v>
+      </c>
+      <c r="D26" s="11">
+        <v>150</v>
+      </c>
+      <c r="E26" s="11">
+        <v>100</v>
+      </c>
+      <c r="F26" s="11">
+        <v>300</v>
+      </c>
+      <c r="G26" s="11">
+        <v>5</v>
+      </c>
+      <c r="H26" s="11">
+        <v>175</v>
+      </c>
+      <c r="I26" s="6">
+        <f t="shared" si="0"/>
+        <v>1075</v>
+      </c>
+      <c r="J26" s="6">
+        <f t="shared" si="1"/>
+        <v>365</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N26" s="14" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CCF225-71F0-404A-9379-A58A0D86D324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323AE8AB-635B-4A4E-B84C-A6FD78C46B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="51">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>FOCUSED ON STUDY</t>
+  </si>
+  <si>
+    <t>ENERGETIC DAY</t>
   </si>
 </sst>
 </file>
@@ -774,7 +777,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="5">
-        <f t="shared" ref="I6:I26" si="0">SUM(B6:F6,H6)</f>
+        <f t="shared" ref="I6:I27" si="0">SUM(B6:F6,H6)</f>
         <v>1090</v>
       </c>
       <c r="J6" s="5">
@@ -870,7 +873,7 @@
         <v>1115</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" ref="J8:J26" si="1">1440-I8</f>
+        <f t="shared" ref="J8:J27" si="1">1440-I8</f>
         <v>325</v>
       </c>
       <c r="K8" s="11" t="s">
@@ -1718,19 +1721,47 @@
       <c r="A27" s="10">
         <v>46274</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="14"/>
+      <c r="B27" s="11">
+        <v>370</v>
+      </c>
+      <c r="C27" s="11">
+        <v>65</v>
+      </c>
+      <c r="D27" s="11">
+        <v>120</v>
+      </c>
+      <c r="E27" s="11">
+        <v>110</v>
+      </c>
+      <c r="F27" s="11">
+        <v>300</v>
+      </c>
+      <c r="G27" s="11">
+        <v>5</v>
+      </c>
+      <c r="H27" s="11">
+        <v>160</v>
+      </c>
+      <c r="I27" s="6">
+        <f t="shared" si="0"/>
+        <v>1125</v>
+      </c>
+      <c r="J27" s="6">
+        <f t="shared" si="1"/>
+        <v>315</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N27" s="14" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323AE8AB-635B-4A4E-B84C-A6FD78C46B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC95C6E4-4FD8-4090-A7F1-DBFAA8739047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="52">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -189,6 +189,9 @@
   </si>
   <si>
     <t>ENERGETIC DAY</t>
+  </si>
+  <si>
+    <t>ENJOYED FRESHER'S PARTY</t>
   </si>
 </sst>
 </file>
@@ -777,7 +780,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="5">
-        <f t="shared" ref="I6:I27" si="0">SUM(B6:F6,H6)</f>
+        <f t="shared" ref="I6:I28" si="0">SUM(B6:F6,H6)</f>
         <v>1090</v>
       </c>
       <c r="J6" s="5">
@@ -873,7 +876,7 @@
         <v>1115</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" ref="J8:J27" si="1">1440-I8</f>
+        <f t="shared" ref="J8:J28" si="1">1440-I8</f>
         <v>325</v>
       </c>
       <c r="K8" s="11" t="s">
@@ -1767,19 +1770,47 @@
       <c r="A28" s="10">
         <v>46275</v>
       </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="14"/>
+      <c r="B28" s="11">
+        <v>300</v>
+      </c>
+      <c r="C28" s="11">
+        <v>50</v>
+      </c>
+      <c r="D28" s="11">
+        <v>110</v>
+      </c>
+      <c r="E28" s="11">
+        <v>95</v>
+      </c>
+      <c r="F28" s="11">
+        <v>370</v>
+      </c>
+      <c r="G28" s="11">
+        <v>6</v>
+      </c>
+      <c r="H28" s="11">
+        <v>185</v>
+      </c>
+      <c r="I28" s="6">
+        <f t="shared" si="0"/>
+        <v>1110</v>
+      </c>
+      <c r="J28" s="6">
+        <f t="shared" si="1"/>
+        <v>330</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N28" s="14" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
